--- a/data/trans_bre/IQ26A_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,08</t>
+          <t>21,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 12,24</t>
+          <t>-5,78; 11,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 8,02</t>
+          <t>-6,62; 8,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 12,75</t>
+          <t>-9,19; 12,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 43,46</t>
+          <t>4,88; 46,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 112,28</t>
+          <t>-33,3; 111,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 129,82</t>
+          <t>-47,8; 129,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 145,04</t>
+          <t>-51,6; 141,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,22</t>
+          <t>-2,42; 4,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 1,27</t>
+          <t>-5,53; 1,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,42</t>
+          <t>-3,35; 4,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 13,18</t>
+          <t>-9,57; 10,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 42,52</t>
+          <t>-18,71; 45,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 12,34</t>
+          <t>-40,68; 11,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 35,66</t>
+          <t>-21,22; 35,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 93,32</t>
+          <t>-39,23; 67,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,5</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 8,44</t>
+          <t>-4,52; 7,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 8,49</t>
+          <t>-3,34; 7,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 5,21</t>
+          <t>-7,2; 5,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 25,29</t>
+          <t>-3,26; 24,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 86,69</t>
+          <t>-28,0; 85,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 130,75</t>
+          <t>-29,24; 118,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 42,24</t>
+          <t>-38,55; 38,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 227,15</t>
+          <t>-14,03; 210,46</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,36</t>
+          <t>-1,31; 4,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,19</t>
+          <t>-3,3; 2,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,97</t>
+          <t>-2,61; 3,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 14,41</t>
+          <t>-2,84; 13,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 42,15</t>
+          <t>-9,57; 39,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 23,38</t>
+          <t>-26,06; 23,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 23,99</t>
+          <t>-16,69; 27,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 95,36</t>
+          <t>-13,09; 91,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ26A_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>2.872880913109841</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7887227507121897</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.279434352165337</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>21.89237440223076</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1957862914609743</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0769984972710524</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.09491084207783942</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,166 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,78; 11,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,62; 8,39</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,19; 12,3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,88; 46,71</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-33,3; 111,43</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-47,8; 129,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-51,6; 141,57</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.782922659872919</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.61979682817094</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-9.192903102308579</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.882361779575349</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3330037194372901</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4779773009950216</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5159562764902811</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.39217052754986</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.389974361025955</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.30244702453009</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>46.70636587260373</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.114289147813479</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.295760361102995</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.415737577495507</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-16,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 4,51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,53; 1,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,35; 4,32</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,57; 10,92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-18,71; 45,55</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-40,68; 11,53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-21,22; 35,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-39,23; 67,65</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.9409529400735015</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.98308043012175</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3447370289099805</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.1756515812723847</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.082959810221765</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1676091701027181</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02450422897216661</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.008467324268603048</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-7,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>60,71%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.415388315991685</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.530545692419836</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.348086284180487</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.57169334418206</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1871365049152744</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4067601543359423</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2122477610749707</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3922659720617334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 7,58</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 7,94</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 5,17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,26; 24,96</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-28,0; 85,84</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-29,24; 118,43</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-38,55; 38,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-14,03; 210,46</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.507994697713054</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.101621681601719</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.324916769292661</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.9222632863381</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4554928193725761</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1152610578596076</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.357285516640077</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.67647592812596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +817,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,85</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-5,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.707357867859105</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.631854875348756</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.182560092844892</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10.98230098908043</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1303254528857157</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2815102038423078</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.07328820703626376</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.6071317787420538</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,31; 4,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 2,3</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 3,55</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 13,85</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-9,57; 39,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-26,06; 23,4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-16,69; 27,58</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-13,09; 91,52</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.524294107995559</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.34442809625151</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.203655615066797</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.26244996880042</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.280029201000155</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2924408142942073</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3855102842534179</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1403098103297044</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.580234230459699</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.938870615180088</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.17194664422782</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>24.95565043897478</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8583850837771528</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.184285270139822</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3867469853635205</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.104612184998789</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.509020604942443</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5845819369267049</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04942356508404744</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.849190175198132</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1244692003122195</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.05273957125960142</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.003402635782513513</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.2592756608485701</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.313880692824043</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.295170808425292</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.611929340832301</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.840517901503463</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.095728661520388</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2605879762028681</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1668754702910007</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.130877930817925</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.155436640955638</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.300941354599595</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.547064705075733</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>13.8530238253774</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3954862804165824</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2340266141999775</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.275846228217617</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9152031828519622</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1015,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
